--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1048,1655 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127399725</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95796</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>557881</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6461180</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127399720</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95796</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>557888</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6461208</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127399709</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>557828</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6461278</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127399712</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>557855</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6461214</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127399721</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95796</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>557884</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6461188</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127399707</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>557879</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6461294</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127399728</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100625</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>557906</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6460932</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127399727</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100625</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>557937</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6460931</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127399710</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>557834</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6461267</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127399715</v>
+      </c>
+      <c r="B14" t="n">
+        <v>95939</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>557855</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6461214</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127399717</v>
+      </c>
+      <c r="B15" t="n">
+        <v>95796</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>557863</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6461210</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127399716</v>
+      </c>
+      <c r="B16" t="n">
+        <v>95939</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>557860</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6461212</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127399723</v>
+      </c>
+      <c r="B17" t="n">
+        <v>95939</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>557874</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6461193</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127399708</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4985</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100307</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blompraktbagge</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Anthaxia morio</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>557825</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6461277</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127399718</v>
+      </c>
+      <c r="B19" t="n">
+        <v>95939</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>557887</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6461210</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127399706</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>557932</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6461352</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127399713</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8436</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>557855</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6461214</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1826,32 +1826,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127399710</v>
+        <v>127399715</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>95939</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557834</v>
+        <v>557855</v>
       </c>
       <c r="R13" t="n">
-        <v>6461267</v>
+        <v>6461214</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1923,32 +1923,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127399715</v>
+        <v>127399710</v>
       </c>
       <c r="B14" t="n">
-        <v>95939</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557855</v>
+        <v>557834</v>
       </c>
       <c r="R14" t="n">
-        <v>6461214</v>
+        <v>6461267</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127399725</v>
+        <v>127399720</v>
       </c>
       <c r="B5" t="n">
-        <v>95796</v>
+        <v>95800</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557881</v>
+        <v>557888</v>
       </c>
       <c r="R5" t="n">
-        <v>6461180</v>
+        <v>6461208</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1147,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127399720</v>
+        <v>127399725</v>
       </c>
       <c r="B6" t="n">
-        <v>95796</v>
+        <v>95800</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557888</v>
+        <v>557881</v>
       </c>
       <c r="R6" t="n">
-        <v>6461208</v>
+        <v>6461180</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1247,7 +1247,7 @@
         <v>127399709</v>
       </c>
       <c r="B7" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,32 +1341,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127399712</v>
+        <v>127399721</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>95800</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557855</v>
+        <v>557884</v>
       </c>
       <c r="R8" t="n">
-        <v>6461214</v>
+        <v>6461188</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1438,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127399721</v>
+        <v>127399712</v>
       </c>
       <c r="B9" t="n">
-        <v>95796</v>
+        <v>57658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557884</v>
+        <v>557855</v>
       </c>
       <c r="R9" t="n">
-        <v>6461188</v>
+        <v>6461214</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1538,7 +1538,7 @@
         <v>127399707</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>127399728</v>
       </c>
       <c r="B11" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>127399727</v>
       </c>
       <c r="B12" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>127399715</v>
       </c>
       <c r="B13" t="n">
-        <v>95939</v>
+        <v>95943</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>127399710</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>127399717</v>
       </c>
       <c r="B15" t="n">
-        <v>95796</v>
+        <v>95800</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127399716</v>
+        <v>127399723</v>
       </c>
       <c r="B16" t="n">
-        <v>95939</v>
+        <v>95943</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557860</v>
+        <v>557874</v>
       </c>
       <c r="R16" t="n">
-        <v>6461212</v>
+        <v>6461193</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127399723</v>
+        <v>127399716</v>
       </c>
       <c r="B17" t="n">
-        <v>95939</v>
+        <v>95943</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557874</v>
+        <v>557860</v>
       </c>
       <c r="R17" t="n">
-        <v>6461193</v>
+        <v>6461212</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2314,7 +2314,7 @@
         <v>127399708</v>
       </c>
       <c r="B18" t="n">
-        <v>4985</v>
+        <v>4986</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,32 +2408,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127399718</v>
+        <v>127399706</v>
       </c>
       <c r="B19" t="n">
-        <v>95939</v>
+        <v>78776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557887</v>
+        <v>557932</v>
       </c>
       <c r="R19" t="n">
-        <v>6461210</v>
+        <v>6461352</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,32 +2505,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127399706</v>
+        <v>127399718</v>
       </c>
       <c r="B20" t="n">
-        <v>78772</v>
+        <v>95943</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>2170</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557932</v>
+        <v>557887</v>
       </c>
       <c r="R20" t="n">
-        <v>6461352</v>
+        <v>6461210</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2605,7 +2605,7 @@
         <v>127399713</v>
       </c>
       <c r="B21" t="n">
-        <v>8436</v>
+        <v>8439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127399720</v>
+        <v>127399725</v>
       </c>
       <c r="B5" t="n">
         <v>95800</v>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557888</v>
+        <v>557881</v>
       </c>
       <c r="R5" t="n">
-        <v>6461208</v>
+        <v>6461180</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127399725</v>
+        <v>127399720</v>
       </c>
       <c r="B6" t="n">
         <v>95800</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557881</v>
+        <v>557888</v>
       </c>
       <c r="R6" t="n">
-        <v>6461180</v>
+        <v>6461208</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127399723</v>
+        <v>127399716</v>
       </c>
       <c r="B16" t="n">
         <v>95943</v>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557874</v>
+        <v>557860</v>
       </c>
       <c r="R16" t="n">
-        <v>6461193</v>
+        <v>6461212</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127399716</v>
+        <v>127399723</v>
       </c>
       <c r="B17" t="n">
         <v>95943</v>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557860</v>
+        <v>557874</v>
       </c>
       <c r="R17" t="n">
-        <v>6461212</v>
+        <v>6461193</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2408,32 +2408,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127399706</v>
+        <v>127399718</v>
       </c>
       <c r="B19" t="n">
-        <v>78776</v>
+        <v>95943</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>2170</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557932</v>
+        <v>557887</v>
       </c>
       <c r="R19" t="n">
-        <v>6461352</v>
+        <v>6461210</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,32 +2505,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127399718</v>
+        <v>127399706</v>
       </c>
       <c r="B20" t="n">
-        <v>95943</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2170</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557887</v>
+        <v>557932</v>
       </c>
       <c r="R20" t="n">
-        <v>6461210</v>
+        <v>6461352</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1635,7 +1635,7 @@
         <v>127399728</v>
       </c>
       <c r="B11" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>127399727</v>
       </c>
       <c r="B12" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2408,32 +2408,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127399718</v>
+        <v>127399706</v>
       </c>
       <c r="B19" t="n">
-        <v>95943</v>
+        <v>78776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557887</v>
+        <v>557932</v>
       </c>
       <c r="R19" t="n">
-        <v>6461210</v>
+        <v>6461352</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,32 +2505,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127399706</v>
+        <v>127399718</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>95943</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>2170</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557932</v>
+        <v>557887</v>
       </c>
       <c r="R20" t="n">
-        <v>6461352</v>
+        <v>6461210</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>127399725</v>
       </c>
       <c r="B5" t="n">
-        <v>95800</v>
+        <v>95802</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>127399720</v>
       </c>
       <c r="B6" t="n">
-        <v>95800</v>
+        <v>95802</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127399709</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,32 +1341,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127399721</v>
+        <v>127399712</v>
       </c>
       <c r="B8" t="n">
-        <v>95800</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557884</v>
+        <v>557855</v>
       </c>
       <c r="R8" t="n">
-        <v>6461188</v>
+        <v>6461214</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1438,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127399712</v>
+        <v>127399721</v>
       </c>
       <c r="B9" t="n">
-        <v>57658</v>
+        <v>95802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557855</v>
+        <v>557884</v>
       </c>
       <c r="R9" t="n">
-        <v>6461214</v>
+        <v>6461188</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1635,7 +1635,7 @@
         <v>127399728</v>
       </c>
       <c r="B11" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>127399727</v>
       </c>
       <c r="B12" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,32 +1826,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127399715</v>
+        <v>127399710</v>
       </c>
       <c r="B13" t="n">
-        <v>95943</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557855</v>
+        <v>557834</v>
       </c>
       <c r="R13" t="n">
-        <v>6461214</v>
+        <v>6461267</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1923,32 +1923,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127399710</v>
+        <v>127399715</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
+        <v>95945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557834</v>
+        <v>557855</v>
       </c>
       <c r="R14" t="n">
-        <v>6461267</v>
+        <v>6461214</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2023,7 +2023,7 @@
         <v>127399717</v>
       </c>
       <c r="B15" t="n">
-        <v>95800</v>
+        <v>95802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>127399716</v>
       </c>
       <c r="B16" t="n">
-        <v>95943</v>
+        <v>95945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>127399723</v>
       </c>
       <c r="B17" t="n">
-        <v>95943</v>
+        <v>95945</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,32 +2408,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127399706</v>
+        <v>127399718</v>
       </c>
       <c r="B19" t="n">
-        <v>78776</v>
+        <v>95945</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>2170</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557932</v>
+        <v>557887</v>
       </c>
       <c r="R19" t="n">
-        <v>6461352</v>
+        <v>6461210</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,32 +2505,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127399718</v>
+        <v>127399706</v>
       </c>
       <c r="B20" t="n">
-        <v>95943</v>
+        <v>78778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2170</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557887</v>
+        <v>557932</v>
       </c>
       <c r="R20" t="n">
-        <v>6461210</v>
+        <v>6461352</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1826,32 +1826,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127399710</v>
+        <v>127399715</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>95945</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557834</v>
+        <v>557855</v>
       </c>
       <c r="R13" t="n">
-        <v>6461267</v>
+        <v>6461214</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1923,32 +1923,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127399715</v>
+        <v>127399710</v>
       </c>
       <c r="B14" t="n">
-        <v>95945</v>
+        <v>79638</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557855</v>
+        <v>557834</v>
       </c>
       <c r="R14" t="n">
-        <v>6461214</v>
+        <v>6461267</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1341,32 +1341,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127399712</v>
+        <v>127399721</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>95802</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557855</v>
+        <v>557884</v>
       </c>
       <c r="R8" t="n">
-        <v>6461214</v>
+        <v>6461188</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1438,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127399721</v>
+        <v>127399712</v>
       </c>
       <c r="B9" t="n">
-        <v>95802</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557884</v>
+        <v>557855</v>
       </c>
       <c r="R9" t="n">
-        <v>6461188</v>
+        <v>6461214</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1826,32 +1826,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127399715</v>
+        <v>127399710</v>
       </c>
       <c r="B13" t="n">
-        <v>95945</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557855</v>
+        <v>557834</v>
       </c>
       <c r="R13" t="n">
-        <v>6461214</v>
+        <v>6461267</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1923,32 +1923,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127399710</v>
+        <v>127399715</v>
       </c>
       <c r="B14" t="n">
-        <v>79638</v>
+        <v>95945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557834</v>
+        <v>557855</v>
       </c>
       <c r="R14" t="n">
-        <v>6461267</v>
+        <v>6461214</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2408,32 +2408,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127399718</v>
+        <v>127399706</v>
       </c>
       <c r="B19" t="n">
-        <v>95945</v>
+        <v>78778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557887</v>
+        <v>557932</v>
       </c>
       <c r="R19" t="n">
-        <v>6461210</v>
+        <v>6461352</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,32 +2505,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127399706</v>
+        <v>127399718</v>
       </c>
       <c r="B20" t="n">
-        <v>78778</v>
+        <v>95945</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>2170</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557932</v>
+        <v>557887</v>
       </c>
       <c r="R20" t="n">
-        <v>6461352</v>
+        <v>6461210</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>127399725</v>
       </c>
       <c r="B5" t="n">
-        <v>95802</v>
+        <v>95808</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>127399720</v>
       </c>
       <c r="B6" t="n">
-        <v>95802</v>
+        <v>95808</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127399721</v>
       </c>
       <c r="B8" t="n">
-        <v>95802</v>
+        <v>95808</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>127399728</v>
       </c>
       <c r="B11" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>127399727</v>
       </c>
       <c r="B12" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,32 +1826,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127399710</v>
+        <v>127399715</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>95951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557834</v>
+        <v>557855</v>
       </c>
       <c r="R13" t="n">
-        <v>6461267</v>
+        <v>6461214</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1923,32 +1923,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127399715</v>
+        <v>127399710</v>
       </c>
       <c r="B14" t="n">
-        <v>95945</v>
+        <v>79638</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557855</v>
+        <v>557834</v>
       </c>
       <c r="R14" t="n">
-        <v>6461214</v>
+        <v>6461267</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2023,7 +2023,7 @@
         <v>127399717</v>
       </c>
       <c r="B15" t="n">
-        <v>95802</v>
+        <v>95808</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>127399716</v>
       </c>
       <c r="B16" t="n">
-        <v>95945</v>
+        <v>95951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>127399723</v>
       </c>
       <c r="B17" t="n">
-        <v>95945</v>
+        <v>95951</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,32 +2408,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127399706</v>
+        <v>127399718</v>
       </c>
       <c r="B19" t="n">
-        <v>78778</v>
+        <v>95951</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>2170</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557932</v>
+        <v>557887</v>
       </c>
       <c r="R19" t="n">
-        <v>6461352</v>
+        <v>6461210</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,32 +2505,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127399718</v>
+        <v>127399706</v>
       </c>
       <c r="B20" t="n">
-        <v>95945</v>
+        <v>78778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2170</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557887</v>
+        <v>557932</v>
       </c>
       <c r="R20" t="n">
-        <v>6461210</v>
+        <v>6461352</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>127399725</v>
       </c>
       <c r="B5" t="n">
-        <v>95808</v>
+        <v>95811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>127399720</v>
       </c>
       <c r="B6" t="n">
-        <v>95808</v>
+        <v>95811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127399709</v>
       </c>
       <c r="B7" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127399721</v>
       </c>
       <c r="B8" t="n">
-        <v>95808</v>
+        <v>95811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>127399712</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>127399728</v>
       </c>
       <c r="B11" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>127399727</v>
       </c>
       <c r="B12" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,32 +1826,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127399715</v>
+        <v>127399710</v>
       </c>
       <c r="B13" t="n">
-        <v>95951</v>
+        <v>79641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557855</v>
+        <v>557834</v>
       </c>
       <c r="R13" t="n">
-        <v>6461214</v>
+        <v>6461267</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1923,32 +1923,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127399710</v>
+        <v>127399715</v>
       </c>
       <c r="B14" t="n">
-        <v>79638</v>
+        <v>95954</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557834</v>
+        <v>557855</v>
       </c>
       <c r="R14" t="n">
-        <v>6461267</v>
+        <v>6461214</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2023,7 +2023,7 @@
         <v>127399717</v>
       </c>
       <c r="B15" t="n">
-        <v>95808</v>
+        <v>95811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>127399716</v>
       </c>
       <c r="B16" t="n">
-        <v>95951</v>
+        <v>95954</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>127399723</v>
       </c>
       <c r="B17" t="n">
-        <v>95951</v>
+        <v>95954</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>127399718</v>
       </c>
       <c r="B19" t="n">
-        <v>95951</v>
+        <v>95954</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>127399706</v>
       </c>
       <c r="B20" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>127399725</v>
       </c>
       <c r="B5" t="n">
-        <v>95811</v>
+        <v>95819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>127399720</v>
       </c>
       <c r="B6" t="n">
-        <v>95811</v>
+        <v>95819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127399709</v>
       </c>
       <c r="B7" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127399721</v>
       </c>
       <c r="B8" t="n">
-        <v>95811</v>
+        <v>95819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>127399712</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>127399728</v>
       </c>
       <c r="B11" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>127399727</v>
       </c>
       <c r="B12" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>127399710</v>
       </c>
       <c r="B13" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>127399715</v>
       </c>
       <c r="B14" t="n">
-        <v>95954</v>
+        <v>95962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>127399717</v>
       </c>
       <c r="B15" t="n">
-        <v>95811</v>
+        <v>95819</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>127399716</v>
       </c>
       <c r="B16" t="n">
-        <v>95954</v>
+        <v>95962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>127399723</v>
       </c>
       <c r="B17" t="n">
-        <v>95954</v>
+        <v>95962</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,32 +2408,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127399718</v>
+        <v>127399706</v>
       </c>
       <c r="B19" t="n">
-        <v>95954</v>
+        <v>78787</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557887</v>
+        <v>557932</v>
       </c>
       <c r="R19" t="n">
-        <v>6461210</v>
+        <v>6461352</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,32 +2505,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127399706</v>
+        <v>127399718</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>95962</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>2170</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557932</v>
+        <v>557887</v>
       </c>
       <c r="R20" t="n">
-        <v>6461352</v>
+        <v>6461210</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>127399725</v>
       </c>
       <c r="B5" t="n">
-        <v>95819</v>
+        <v>95820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>127399720</v>
       </c>
       <c r="B6" t="n">
-        <v>95819</v>
+        <v>95820</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127399721</v>
       </c>
       <c r="B8" t="n">
-        <v>95819</v>
+        <v>95820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>127399728</v>
       </c>
       <c r="B11" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>127399727</v>
       </c>
       <c r="B12" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>127399715</v>
       </c>
       <c r="B14" t="n">
-        <v>95962</v>
+        <v>95963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>127399717</v>
       </c>
       <c r="B15" t="n">
-        <v>95819</v>
+        <v>95820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>127399716</v>
       </c>
       <c r="B16" t="n">
-        <v>95962</v>
+        <v>95963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>127399723</v>
       </c>
       <c r="B17" t="n">
-        <v>95962</v>
+        <v>95963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,32 +2408,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127399706</v>
+        <v>127399718</v>
       </c>
       <c r="B19" t="n">
-        <v>78787</v>
+        <v>95963</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>2170</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557932</v>
+        <v>557887</v>
       </c>
       <c r="R19" t="n">
-        <v>6461352</v>
+        <v>6461210</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,32 +2505,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127399718</v>
+        <v>127399706</v>
       </c>
       <c r="B20" t="n">
-        <v>95962</v>
+        <v>78787</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2170</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557887</v>
+        <v>557932</v>
       </c>
       <c r="R20" t="n">
-        <v>6461210</v>
+        <v>6461352</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1341,32 +1341,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127399721</v>
+        <v>127399712</v>
       </c>
       <c r="B8" t="n">
-        <v>95820</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557884</v>
+        <v>557855</v>
       </c>
       <c r="R8" t="n">
-        <v>6461188</v>
+        <v>6461214</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1438,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127399712</v>
+        <v>127399721</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>95820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557855</v>
+        <v>557884</v>
       </c>
       <c r="R9" t="n">
-        <v>6461214</v>
+        <v>6461188</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -2408,32 +2408,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127399718</v>
+        <v>127399706</v>
       </c>
       <c r="B19" t="n">
-        <v>95963</v>
+        <v>78787</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557887</v>
+        <v>557932</v>
       </c>
       <c r="R19" t="n">
-        <v>6461210</v>
+        <v>6461352</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,32 +2505,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127399706</v>
+        <v>127399718</v>
       </c>
       <c r="B20" t="n">
-        <v>78787</v>
+        <v>95963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>2170</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557932</v>
+        <v>557887</v>
       </c>
       <c r="R20" t="n">
-        <v>6461352</v>
+        <v>6461210</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>127399725</v>
       </c>
       <c r="B5" t="n">
-        <v>95820</v>
+        <v>95821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>127399720</v>
       </c>
       <c r="B6" t="n">
-        <v>95820</v>
+        <v>95821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1341,32 +1341,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127399712</v>
+        <v>127399721</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>95821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557855</v>
+        <v>557884</v>
       </c>
       <c r="R8" t="n">
-        <v>6461214</v>
+        <v>6461188</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1438,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127399721</v>
+        <v>127399712</v>
       </c>
       <c r="B9" t="n">
-        <v>95820</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557884</v>
+        <v>557855</v>
       </c>
       <c r="R9" t="n">
-        <v>6461188</v>
+        <v>6461214</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1635,7 +1635,7 @@
         <v>127399728</v>
       </c>
       <c r="B11" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>127399727</v>
       </c>
       <c r="B12" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,32 +1826,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127399710</v>
+        <v>127399715</v>
       </c>
       <c r="B13" t="n">
-        <v>79647</v>
+        <v>95964</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557834</v>
+        <v>557855</v>
       </c>
       <c r="R13" t="n">
-        <v>6461267</v>
+        <v>6461214</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1923,32 +1923,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127399715</v>
+        <v>127399710</v>
       </c>
       <c r="B14" t="n">
-        <v>95963</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557855</v>
+        <v>557834</v>
       </c>
       <c r="R14" t="n">
-        <v>6461214</v>
+        <v>6461267</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2023,7 +2023,7 @@
         <v>127399717</v>
       </c>
       <c r="B15" t="n">
-        <v>95820</v>
+        <v>95821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>127399716</v>
       </c>
       <c r="B16" t="n">
-        <v>95963</v>
+        <v>95964</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>127399723</v>
       </c>
       <c r="B17" t="n">
-        <v>95963</v>
+        <v>95964</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,32 +2408,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127399706</v>
+        <v>127399718</v>
       </c>
       <c r="B19" t="n">
-        <v>78787</v>
+        <v>95964</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>2170</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557932</v>
+        <v>557887</v>
       </c>
       <c r="R19" t="n">
-        <v>6461352</v>
+        <v>6461210</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,32 +2505,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127399718</v>
+        <v>127399706</v>
       </c>
       <c r="B20" t="n">
-        <v>95963</v>
+        <v>78787</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2170</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557887</v>
+        <v>557932</v>
       </c>
       <c r="R20" t="n">
-        <v>6461210</v>
+        <v>6461352</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>127399725</v>
       </c>
       <c r="B5" t="n">
-        <v>95821</v>
+        <v>95822</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>127399720</v>
       </c>
       <c r="B6" t="n">
-        <v>95821</v>
+        <v>95822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127399721</v>
       </c>
       <c r="B8" t="n">
-        <v>95821</v>
+        <v>95822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>127399728</v>
       </c>
       <c r="B11" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>127399727</v>
       </c>
       <c r="B12" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,32 +1826,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127399715</v>
+        <v>127399710</v>
       </c>
       <c r="B13" t="n">
-        <v>95964</v>
+        <v>79647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557855</v>
+        <v>557834</v>
       </c>
       <c r="R13" t="n">
-        <v>6461214</v>
+        <v>6461267</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1923,32 +1923,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127399710</v>
+        <v>127399715</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>95965</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557834</v>
+        <v>557855</v>
       </c>
       <c r="R14" t="n">
-        <v>6461267</v>
+        <v>6461214</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2023,7 +2023,7 @@
         <v>127399717</v>
       </c>
       <c r="B15" t="n">
-        <v>95821</v>
+        <v>95822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>127399716</v>
       </c>
       <c r="B16" t="n">
-        <v>95964</v>
+        <v>95965</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>127399723</v>
       </c>
       <c r="B17" t="n">
-        <v>95964</v>
+        <v>95965</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>127399718</v>
       </c>
       <c r="B19" t="n">
-        <v>95964</v>
+        <v>95965</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2408,32 +2408,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127399718</v>
+        <v>127399706</v>
       </c>
       <c r="B19" t="n">
-        <v>95965</v>
+        <v>78787</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557887</v>
+        <v>557932</v>
       </c>
       <c r="R19" t="n">
-        <v>6461210</v>
+        <v>6461352</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,32 +2505,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127399706</v>
+        <v>127399718</v>
       </c>
       <c r="B20" t="n">
-        <v>78787</v>
+        <v>95965</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>2170</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557932</v>
+        <v>557887</v>
       </c>
       <c r="R20" t="n">
-        <v>6461352</v>
+        <v>6461210</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127399725</v>
+        <v>127399720</v>
       </c>
       <c r="B5" t="n">
         <v>95822</v>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557881</v>
+        <v>557888</v>
       </c>
       <c r="R5" t="n">
-        <v>6461180</v>
+        <v>6461208</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127399720</v>
+        <v>127399725</v>
       </c>
       <c r="B6" t="n">
         <v>95822</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557888</v>
+        <v>557881</v>
       </c>
       <c r="R6" t="n">
-        <v>6461208</v>
+        <v>6461180</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2697,6 +2697,2105 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129372672</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>557761</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6460898</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>färska och äldre hack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129373539</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92874</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>557822</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6461312</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129373239</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>557888</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6461234</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129373315</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>557831</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6461322</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Revirparet i sitt permanenta revir respektive i viktig del av reviret.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129373250</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79660</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>557837</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6461265</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129373370</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92874</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>557786</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6461383</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129373253</v>
+      </c>
+      <c r="B28" t="n">
+        <v>81026</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>557837</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6461265</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129372647</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79660</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>557761</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6460898</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129373262</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92178</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>557835</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6461268</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129373243</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79660</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>557858</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6461263</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129373551</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79660</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>557913</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6461341</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129373521</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92874</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>557768</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6461405</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129373557</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79660</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>557914</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6461343</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129373573</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>557883</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6461355</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hane i sitt permanenta revir hackandes på en äldre asplåga.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129373230</v>
+      </c>
+      <c r="B36" t="n">
+        <v>75159</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>557888</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6461234</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129373529</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92874</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>557783</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6461366</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129373216</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78444</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>557861</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6461205</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129373273</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92874</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>557842</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6461313</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129373098</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>557884</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6461195</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129373119</v>
+      </c>
+      <c r="B41" t="n">
+        <v>96130</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>210</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>557870</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6461202</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2812,7 +2812,7 @@
         <v>129373539</v>
       </c>
       <c r="B23" t="n">
-        <v>92874</v>
+        <v>92859</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>129373370</v>
       </c>
       <c r="B27" t="n">
-        <v>92874</v>
+        <v>92859</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>129373262</v>
       </c>
       <c r="B30" t="n">
-        <v>92178</v>
+        <v>92192</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>129373521</v>
       </c>
       <c r="B33" t="n">
-        <v>92874</v>
+        <v>92859</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4176,35 +4176,39 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129373230</v>
+        <v>129373529</v>
       </c>
       <c r="B36" t="n">
-        <v>75159</v>
+        <v>92859</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4214,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557888</v>
+        <v>557783</v>
       </c>
       <c r="R36" t="n">
-        <v>6461234</v>
+        <v>6461366</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4277,39 +4281,35 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129373529</v>
+        <v>129373230</v>
       </c>
       <c r="B37" t="n">
-        <v>92874</v>
+        <v>75159</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557783</v>
+        <v>557888</v>
       </c>
       <c r="R37" t="n">
-        <v>6461366</v>
+        <v>6461234</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129373216</v>
+        <v>129373273</v>
       </c>
       <c r="B38" t="n">
-        <v>78444</v>
+        <v>92859</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,24 +4393,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4420,10 +4424,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557861</v>
+        <v>557842</v>
       </c>
       <c r="R38" t="n">
-        <v>6461205</v>
+        <v>6461313</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,11 +4460,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4488,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129373273</v>
+        <v>129373216</v>
       </c>
       <c r="B39" t="n">
-        <v>92874</v>
+        <v>78444</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4499,28 +4498,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4530,10 +4525,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557842</v>
+        <v>557861</v>
       </c>
       <c r="R39" t="n">
-        <v>6461313</v>
+        <v>6461205</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,6 +4561,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4699,7 +4699,7 @@
         <v>129373119</v>
       </c>
       <c r="B41" t="n">
-        <v>96130</v>
+        <v>96146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2812,7 +2812,7 @@
         <v>129373539</v>
       </c>
       <c r="B23" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3137,10 +3137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129373250</v>
+        <v>129373370</v>
       </c>
       <c r="B26" t="n">
-        <v>79660</v>
+        <v>92860</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,24 +3148,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3175,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557837</v>
+        <v>557786</v>
       </c>
       <c r="R26" t="n">
-        <v>6461265</v>
+        <v>6461383</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,10 +3242,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129373370</v>
+        <v>129373250</v>
       </c>
       <c r="B27" t="n">
-        <v>92859</v>
+        <v>79660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,28 +3253,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557786</v>
+        <v>557837</v>
       </c>
       <c r="R27" t="n">
-        <v>6461383</v>
+        <v>6461265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
         <v>129373262</v>
       </c>
       <c r="B30" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>129373521</v>
       </c>
       <c r="B33" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4176,39 +4176,35 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129373529</v>
+        <v>129373230</v>
       </c>
       <c r="B36" t="n">
-        <v>92859</v>
+        <v>75159</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4218,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557783</v>
+        <v>557888</v>
       </c>
       <c r="R36" t="n">
-        <v>6461366</v>
+        <v>6461234</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4281,35 +4277,39 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129373230</v>
+        <v>129373529</v>
       </c>
       <c r="B37" t="n">
-        <v>75159</v>
+        <v>92860</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557888</v>
+        <v>557783</v>
       </c>
       <c r="R37" t="n">
-        <v>6461234</v>
+        <v>6461366</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4385,7 +4385,7 @@
         <v>129373273</v>
       </c>
       <c r="B38" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>129373119</v>
       </c>
       <c r="B41" t="n">
-        <v>96146</v>
+        <v>96147</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4176,35 +4176,39 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129373230</v>
+        <v>129373529</v>
       </c>
       <c r="B36" t="n">
-        <v>75159</v>
+        <v>92860</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4214,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557888</v>
+        <v>557783</v>
       </c>
       <c r="R36" t="n">
-        <v>6461234</v>
+        <v>6461366</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4277,39 +4281,35 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129373529</v>
+        <v>129373230</v>
       </c>
       <c r="B37" t="n">
-        <v>92860</v>
+        <v>75159</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557783</v>
+        <v>557888</v>
       </c>
       <c r="R37" t="n">
-        <v>6461366</v>
+        <v>6461234</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4699,7 +4699,7 @@
         <v>129373119</v>
       </c>
       <c r="B41" t="n">
-        <v>96147</v>
+        <v>96148</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4796,6 +4796,538 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129425252</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Herrsätter, Ög</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>557720</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6461009</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129425498</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79660</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Herrsätter, Ög</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>557870</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6461347</v>
+      </c>
+      <c r="S43" t="n">
+        <v>100</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129425231</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Herrsätter, Ög</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>557727</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6461009</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129425486</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92193</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Herrsätter, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>557860</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6461363</v>
+      </c>
+      <c r="S45" t="n">
+        <v>100</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129425154</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Herrsätter, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>557727</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6460998</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2812,7 +2812,7 @@
         <v>129373539</v>
       </c>
       <c r="B23" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3137,10 +3137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129373370</v>
+        <v>129373250</v>
       </c>
       <c r="B26" t="n">
-        <v>92860</v>
+        <v>79662</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,28 +3148,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3179,10 +3175,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557786</v>
+        <v>557837</v>
       </c>
       <c r="R26" t="n">
-        <v>6461383</v>
+        <v>6461265</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3242,10 +3238,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129373250</v>
+        <v>129373370</v>
       </c>
       <c r="B27" t="n">
-        <v>79660</v>
+        <v>92863</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3253,24 +3249,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557837</v>
+        <v>557786</v>
       </c>
       <c r="R27" t="n">
-        <v>6461265</v>
+        <v>6461383</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,7 +3346,7 @@
         <v>129373253</v>
       </c>
       <c r="B28" t="n">
-        <v>81026</v>
+        <v>81028</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>129372647</v>
       </c>
       <c r="B29" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>129373262</v>
       </c>
       <c r="B30" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>129373243</v>
       </c>
       <c r="B31" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129373551</v>
       </c>
       <c r="B32" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>129373521</v>
       </c>
       <c r="B33" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>129373557</v>
       </c>
       <c r="B34" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>129373529</v>
       </c>
       <c r="B36" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>129373230</v>
       </c>
       <c r="B37" t="n">
-        <v>75159</v>
+        <v>75161</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>129373273</v>
       </c>
       <c r="B38" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>129373216</v>
       </c>
       <c r="B39" t="n">
-        <v>78444</v>
+        <v>78446</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>129373119</v>
       </c>
       <c r="B41" t="n">
-        <v>96148</v>
+        <v>96152</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>129425498</v>
       </c>
       <c r="B43" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>129425486</v>
       </c>
       <c r="B45" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>129425154</v>
       </c>
       <c r="B46" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -3137,10 +3137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129373250</v>
+        <v>129373370</v>
       </c>
       <c r="B26" t="n">
-        <v>79662</v>
+        <v>92863</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,24 +3148,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3175,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557837</v>
+        <v>557786</v>
       </c>
       <c r="R26" t="n">
-        <v>6461265</v>
+        <v>6461383</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,10 +3242,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129373370</v>
+        <v>129373250</v>
       </c>
       <c r="B27" t="n">
-        <v>92863</v>
+        <v>79662</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,28 +3253,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557786</v>
+        <v>557837</v>
       </c>
       <c r="R27" t="n">
-        <v>6461383</v>
+        <v>6461265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2812,7 +2812,7 @@
         <v>129373539</v>
       </c>
       <c r="B23" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3137,10 +3137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129373370</v>
+        <v>129373250</v>
       </c>
       <c r="B26" t="n">
-        <v>92863</v>
+        <v>79663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,28 +3148,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3179,10 +3175,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557786</v>
+        <v>557837</v>
       </c>
       <c r="R26" t="n">
-        <v>6461383</v>
+        <v>6461265</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3242,10 +3238,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129373250</v>
+        <v>129373370</v>
       </c>
       <c r="B27" t="n">
-        <v>79662</v>
+        <v>92865</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3253,24 +3249,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557837</v>
+        <v>557786</v>
       </c>
       <c r="R27" t="n">
-        <v>6461265</v>
+        <v>6461383</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129373253</v>
+        <v>129372647</v>
       </c>
       <c r="B28" t="n">
-        <v>81028</v>
+        <v>79663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557837</v>
+        <v>557761</v>
       </c>
       <c r="R28" t="n">
-        <v>6461265</v>
+        <v>6460898</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129372647</v>
+        <v>129373253</v>
       </c>
       <c r="B29" t="n">
-        <v>79662</v>
+        <v>81029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557761</v>
+        <v>557837</v>
       </c>
       <c r="R29" t="n">
-        <v>6460898</v>
+        <v>6461265</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
         <v>129373262</v>
       </c>
       <c r="B30" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>129373243</v>
       </c>
       <c r="B31" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129373551</v>
       </c>
       <c r="B32" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>129373521</v>
       </c>
       <c r="B33" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>129373557</v>
       </c>
       <c r="B34" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,39 +4176,35 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129373529</v>
+        <v>129373230</v>
       </c>
       <c r="B36" t="n">
-        <v>92863</v>
+        <v>75161</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4218,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557783</v>
+        <v>557888</v>
       </c>
       <c r="R36" t="n">
-        <v>6461366</v>
+        <v>6461234</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4281,35 +4277,39 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129373230</v>
+        <v>129373529</v>
       </c>
       <c r="B37" t="n">
-        <v>75161</v>
+        <v>92865</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557888</v>
+        <v>557783</v>
       </c>
       <c r="R37" t="n">
-        <v>6461234</v>
+        <v>6461366</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129373273</v>
+        <v>129373216</v>
       </c>
       <c r="B38" t="n">
-        <v>92863</v>
+        <v>78447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,28 +4393,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4424,10 +4420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557842</v>
+        <v>557861</v>
       </c>
       <c r="R38" t="n">
-        <v>6461313</v>
+        <v>6461205</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4460,6 +4456,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,10 +4488,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129373216</v>
+        <v>129373273</v>
       </c>
       <c r="B39" t="n">
-        <v>78446</v>
+        <v>92865</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4498,24 +4499,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4525,10 +4530,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557861</v>
+        <v>557842</v>
       </c>
       <c r="R39" t="n">
-        <v>6461205</v>
+        <v>6461313</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,11 +4566,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4699,7 +4699,7 @@
         <v>129373119</v>
       </c>
       <c r="B41" t="n">
-        <v>96152</v>
+        <v>96154</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>129425498</v>
       </c>
       <c r="B43" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>129425486</v>
       </c>
       <c r="B45" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>129425154</v>
       </c>
       <c r="B46" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2812,7 +2812,7 @@
         <v>129373539</v>
       </c>
       <c r="B23" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3137,10 +3137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129373250</v>
+        <v>129373370</v>
       </c>
       <c r="B26" t="n">
-        <v>79663</v>
+        <v>92869</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,24 +3148,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3175,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557837</v>
+        <v>557786</v>
       </c>
       <c r="R26" t="n">
-        <v>6461265</v>
+        <v>6461383</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,10 +3242,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129373370</v>
+        <v>129373250</v>
       </c>
       <c r="B27" t="n">
-        <v>92865</v>
+        <v>79663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,28 +3253,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557786</v>
+        <v>557837</v>
       </c>
       <c r="R27" t="n">
-        <v>6461383</v>
+        <v>6461265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
         <v>129373262</v>
       </c>
       <c r="B30" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>129373521</v>
       </c>
       <c r="B33" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4176,35 +4176,39 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129373230</v>
+        <v>129373529</v>
       </c>
       <c r="B36" t="n">
-        <v>75161</v>
+        <v>92869</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4214,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557888</v>
+        <v>557783</v>
       </c>
       <c r="R36" t="n">
-        <v>6461234</v>
+        <v>6461366</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4277,39 +4281,35 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129373529</v>
+        <v>129373230</v>
       </c>
       <c r="B37" t="n">
-        <v>92865</v>
+        <v>75161</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557783</v>
+        <v>557888</v>
       </c>
       <c r="R37" t="n">
-        <v>6461366</v>
+        <v>6461234</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4491,7 +4491,7 @@
         <v>129373273</v>
       </c>
       <c r="B39" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>129373119</v>
       </c>
       <c r="B41" t="n">
-        <v>96154</v>
+        <v>96158</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>129425486</v>
       </c>
       <c r="B45" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>129425154</v>
       </c>
       <c r="B46" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2812,7 +2812,7 @@
         <v>129373539</v>
       </c>
       <c r="B23" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>129373370</v>
       </c>
       <c r="B26" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129372647</v>
+        <v>129373253</v>
       </c>
       <c r="B28" t="n">
-        <v>79663</v>
+        <v>81029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557761</v>
+        <v>557837</v>
       </c>
       <c r="R28" t="n">
-        <v>6460898</v>
+        <v>6461265</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129373253</v>
+        <v>129372647</v>
       </c>
       <c r="B29" t="n">
-        <v>81029</v>
+        <v>79663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557837</v>
+        <v>557761</v>
       </c>
       <c r="R29" t="n">
-        <v>6461265</v>
+        <v>6460898</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
         <v>129373262</v>
       </c>
       <c r="B30" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>129373521</v>
       </c>
       <c r="B33" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>129373529</v>
       </c>
       <c r="B36" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129373216</v>
+        <v>129373273</v>
       </c>
       <c r="B38" t="n">
-        <v>78447</v>
+        <v>92870</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,24 +4393,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4420,10 +4424,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557861</v>
+        <v>557842</v>
       </c>
       <c r="R38" t="n">
-        <v>6461205</v>
+        <v>6461313</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,11 +4460,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4488,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129373273</v>
+        <v>129373216</v>
       </c>
       <c r="B39" t="n">
-        <v>92869</v>
+        <v>78447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4499,28 +4498,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4530,10 +4525,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557842</v>
+        <v>557861</v>
       </c>
       <c r="R39" t="n">
-        <v>6461313</v>
+        <v>6461205</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,6 +4561,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4699,7 +4699,7 @@
         <v>129373119</v>
       </c>
       <c r="B41" t="n">
-        <v>96158</v>
+        <v>96166</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>129425486</v>
       </c>
       <c r="B45" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>129425154</v>
       </c>
       <c r="B46" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2812,7 +2812,7 @@
         <v>129373539</v>
       </c>
       <c r="B23" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>129373370</v>
       </c>
       <c r="B26" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>129373262</v>
       </c>
       <c r="B30" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>129373521</v>
       </c>
       <c r="B33" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>129373529</v>
       </c>
       <c r="B36" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>129373273</v>
       </c>
       <c r="B38" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>129373119</v>
       </c>
       <c r="B41" t="n">
-        <v>96166</v>
+        <v>96169</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>129425486</v>
       </c>
       <c r="B45" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>129425154</v>
       </c>
       <c r="B46" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129373273</v>
+        <v>129373216</v>
       </c>
       <c r="B38" t="n">
-        <v>92873</v>
+        <v>78447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,28 +4393,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4424,10 +4420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557842</v>
+        <v>557861</v>
       </c>
       <c r="R38" t="n">
-        <v>6461313</v>
+        <v>6461205</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4460,6 +4456,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,10 +4488,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129373216</v>
+        <v>129373273</v>
       </c>
       <c r="B39" t="n">
-        <v>78447</v>
+        <v>92873</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4498,24 +4499,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4525,10 +4530,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557861</v>
+        <v>557842</v>
       </c>
       <c r="R39" t="n">
-        <v>6461205</v>
+        <v>6461313</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,11 +4566,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4176,39 +4176,35 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129373529</v>
+        <v>129373230</v>
       </c>
       <c r="B36" t="n">
-        <v>92873</v>
+        <v>75161</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4218,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557783</v>
+        <v>557888</v>
       </c>
       <c r="R36" t="n">
-        <v>6461366</v>
+        <v>6461234</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4281,35 +4277,39 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129373230</v>
+        <v>129373529</v>
       </c>
       <c r="B37" t="n">
-        <v>75161</v>
+        <v>92873</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557888</v>
+        <v>557783</v>
       </c>
       <c r="R37" t="n">
-        <v>6461234</v>
+        <v>6461366</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129373216</v>
+        <v>129373273</v>
       </c>
       <c r="B38" t="n">
-        <v>78447</v>
+        <v>92873</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,24 +4393,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4420,10 +4424,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557861</v>
+        <v>557842</v>
       </c>
       <c r="R38" t="n">
-        <v>6461205</v>
+        <v>6461313</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,11 +4460,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4488,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129373273</v>
+        <v>129373216</v>
       </c>
       <c r="B39" t="n">
-        <v>92873</v>
+        <v>78447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4499,28 +4498,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4530,10 +4525,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557842</v>
+        <v>557861</v>
       </c>
       <c r="R39" t="n">
-        <v>6461313</v>
+        <v>6461205</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,6 +4561,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -3137,10 +3137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129373370</v>
+        <v>129373250</v>
       </c>
       <c r="B26" t="n">
-        <v>92873</v>
+        <v>79663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,28 +3148,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3179,10 +3175,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557786</v>
+        <v>557837</v>
       </c>
       <c r="R26" t="n">
-        <v>6461383</v>
+        <v>6461265</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3242,10 +3238,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129373250</v>
+        <v>129373370</v>
       </c>
       <c r="B27" t="n">
-        <v>79663</v>
+        <v>92873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3253,24 +3249,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557837</v>
+        <v>557786</v>
       </c>
       <c r="R27" t="n">
-        <v>6461265</v>
+        <v>6461383</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129373253</v>
+        <v>129372647</v>
       </c>
       <c r="B28" t="n">
-        <v>81029</v>
+        <v>79663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557837</v>
+        <v>557761</v>
       </c>
       <c r="R28" t="n">
-        <v>6461265</v>
+        <v>6460898</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129372647</v>
+        <v>129373253</v>
       </c>
       <c r="B29" t="n">
-        <v>79663</v>
+        <v>81029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557761</v>
+        <v>557837</v>
       </c>
       <c r="R29" t="n">
-        <v>6460898</v>
+        <v>6461265</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129373273</v>
+        <v>129373216</v>
       </c>
       <c r="B38" t="n">
-        <v>92873</v>
+        <v>78447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,28 +4393,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4424,10 +4420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557842</v>
+        <v>557861</v>
       </c>
       <c r="R38" t="n">
-        <v>6461313</v>
+        <v>6461205</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4460,6 +4456,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,10 +4488,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129373216</v>
+        <v>129373273</v>
       </c>
       <c r="B39" t="n">
-        <v>78447</v>
+        <v>92873</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4498,24 +4499,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4525,10 +4530,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557861</v>
+        <v>557842</v>
       </c>
       <c r="R39" t="n">
-        <v>6461205</v>
+        <v>6461313</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,11 +4566,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,10 +4901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129425498</v>
+        <v>129425231</v>
       </c>
       <c r="B43" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4912,26 +4912,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4939,13 +4956,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557870</v>
+        <v>557727</v>
       </c>
       <c r="R43" t="n">
-        <v>6461347</v>
+        <v>6461009</v>
       </c>
       <c r="S43" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4977,13 +4994,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5002,10 +5023,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129425231</v>
+        <v>129425498</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5013,43 +5034,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5057,13 +5061,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557727</v>
+        <v>557870</v>
       </c>
       <c r="R44" t="n">
-        <v>6461009</v>
+        <v>6461347</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5095,17 +5099,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -3343,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129372647</v>
+        <v>129373253</v>
       </c>
       <c r="B28" t="n">
-        <v>79663</v>
+        <v>81029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557761</v>
+        <v>557837</v>
       </c>
       <c r="R28" t="n">
-        <v>6460898</v>
+        <v>6461265</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129373253</v>
+        <v>129372647</v>
       </c>
       <c r="B29" t="n">
-        <v>81029</v>
+        <v>79663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557837</v>
+        <v>557761</v>
       </c>
       <c r="R29" t="n">
-        <v>6461265</v>
+        <v>6460898</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4176,35 +4176,39 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129373230</v>
+        <v>129373529</v>
       </c>
       <c r="B36" t="n">
-        <v>75161</v>
+        <v>92873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4214,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557888</v>
+        <v>557783</v>
       </c>
       <c r="R36" t="n">
-        <v>6461234</v>
+        <v>6461366</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4277,39 +4281,35 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129373529</v>
+        <v>129373230</v>
       </c>
       <c r="B37" t="n">
-        <v>92873</v>
+        <v>75161</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557783</v>
+        <v>557888</v>
       </c>
       <c r="R37" t="n">
-        <v>6461366</v>
+        <v>6461234</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129373216</v>
+        <v>129373273</v>
       </c>
       <c r="B38" t="n">
-        <v>78447</v>
+        <v>92873</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,24 +4393,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4420,10 +4424,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557861</v>
+        <v>557842</v>
       </c>
       <c r="R38" t="n">
-        <v>6461205</v>
+        <v>6461313</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,11 +4460,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4488,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129373273</v>
+        <v>129373216</v>
       </c>
       <c r="B39" t="n">
-        <v>92873</v>
+        <v>78447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4499,28 +4498,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4530,10 +4525,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557842</v>
+        <v>557861</v>
       </c>
       <c r="R39" t="n">
-        <v>6461313</v>
+        <v>6461205</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,6 +4561,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -3137,10 +3137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129373250</v>
+        <v>129373370</v>
       </c>
       <c r="B26" t="n">
-        <v>79663</v>
+        <v>92873</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,24 +3148,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3175,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557837</v>
+        <v>557786</v>
       </c>
       <c r="R26" t="n">
-        <v>6461265</v>
+        <v>6461383</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,10 +3242,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129373370</v>
+        <v>129373250</v>
       </c>
       <c r="B27" t="n">
-        <v>92873</v>
+        <v>79663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,28 +3253,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557786</v>
+        <v>557837</v>
       </c>
       <c r="R27" t="n">
-        <v>6461383</v>
+        <v>6461265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129425231</v>
+        <v>129425498</v>
       </c>
       <c r="B43" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4912,43 +4912,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4956,13 +4939,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557727</v>
+        <v>557870</v>
       </c>
       <c r="R43" t="n">
-        <v>6461009</v>
+        <v>6461347</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4994,17 +4977,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5023,10 +5002,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129425498</v>
+        <v>129425231</v>
       </c>
       <c r="B44" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5034,26 +5013,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5061,13 +5057,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557870</v>
+        <v>557727</v>
       </c>
       <c r="R44" t="n">
-        <v>6461347</v>
+        <v>6461009</v>
       </c>
       <c r="S44" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5099,13 +5095,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2702,7 +2702,7 @@
         <v>129372672</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>129373539</v>
       </c>
       <c r="B23" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>129373239</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>129373315</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>129373370</v>
       </c>
       <c r="B26" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>129373250</v>
       </c>
       <c r="B27" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>129373253</v>
       </c>
       <c r="B28" t="n">
-        <v>81029</v>
+        <v>81055</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>129372647</v>
       </c>
       <c r="B29" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>129373262</v>
       </c>
       <c r="B30" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>129373243</v>
       </c>
       <c r="B31" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129373551</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>129373521</v>
       </c>
       <c r="B33" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>129373557</v>
       </c>
       <c r="B34" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>129373573</v>
       </c>
       <c r="B35" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4176,39 +4176,35 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129373529</v>
+        <v>129373230</v>
       </c>
       <c r="B36" t="n">
-        <v>92873</v>
+        <v>75182</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4218,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557783</v>
+        <v>557888</v>
       </c>
       <c r="R36" t="n">
-        <v>6461366</v>
+        <v>6461234</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4281,35 +4277,39 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129373230</v>
+        <v>129373529</v>
       </c>
       <c r="B37" t="n">
-        <v>75161</v>
+        <v>92901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557888</v>
+        <v>557783</v>
       </c>
       <c r="R37" t="n">
-        <v>6461234</v>
+        <v>6461366</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129373273</v>
+        <v>129373216</v>
       </c>
       <c r="B38" t="n">
-        <v>92873</v>
+        <v>78473</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,28 +4393,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4424,10 +4420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557842</v>
+        <v>557861</v>
       </c>
       <c r="R38" t="n">
-        <v>6461313</v>
+        <v>6461205</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4460,6 +4456,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,10 +4488,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129373216</v>
+        <v>129373273</v>
       </c>
       <c r="B39" t="n">
-        <v>78447</v>
+        <v>92901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4498,24 +4499,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4525,10 +4530,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557861</v>
+        <v>557842</v>
       </c>
       <c r="R39" t="n">
-        <v>6461205</v>
+        <v>6461313</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,11 +4566,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4699,7 +4699,7 @@
         <v>129373119</v>
       </c>
       <c r="B41" t="n">
-        <v>96169</v>
+        <v>96198</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>129425498</v>
       </c>
       <c r="B43" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>129425231</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>129425486</v>
       </c>
       <c r="B45" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>129425154</v>
       </c>
       <c r="B46" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4176,35 +4176,39 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129373230</v>
+        <v>129373529</v>
       </c>
       <c r="B36" t="n">
-        <v>75182</v>
+        <v>92901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4214,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557888</v>
+        <v>557783</v>
       </c>
       <c r="R36" t="n">
-        <v>6461234</v>
+        <v>6461366</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4277,39 +4281,35 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129373529</v>
+        <v>129373230</v>
       </c>
       <c r="B37" t="n">
-        <v>92901</v>
+        <v>75182</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557783</v>
+        <v>557888</v>
       </c>
       <c r="R37" t="n">
-        <v>6461366</v>
+        <v>6461234</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129425498</v>
+        <v>129425231</v>
       </c>
       <c r="B43" t="n">
-        <v>79689</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4912,26 +4912,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4939,13 +4956,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557870</v>
+        <v>557727</v>
       </c>
       <c r="R43" t="n">
-        <v>6461347</v>
+        <v>6461009</v>
       </c>
       <c r="S43" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4977,13 +4994,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5002,10 +5023,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129425231</v>
+        <v>129425498</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>79689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5013,43 +5034,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5057,13 +5061,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557727</v>
+        <v>557870</v>
       </c>
       <c r="R44" t="n">
-        <v>6461009</v>
+        <v>6461347</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5095,17 +5099,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2702,7 +2702,7 @@
         <v>129372672</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>129373539</v>
       </c>
       <c r="B23" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>129373239</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>129373315</v>
       </c>
       <c r="B25" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>129373370</v>
       </c>
       <c r="B26" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>129373250</v>
       </c>
       <c r="B27" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>129373253</v>
       </c>
       <c r="B28" t="n">
-        <v>81055</v>
+        <v>81060</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>129372647</v>
       </c>
       <c r="B29" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>129373262</v>
       </c>
       <c r="B30" t="n">
-        <v>92234</v>
+        <v>92240</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>129373243</v>
       </c>
       <c r="B31" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129373551</v>
       </c>
       <c r="B32" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>129373521</v>
       </c>
       <c r="B33" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>129373557</v>
       </c>
       <c r="B34" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>129373573</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>129373529</v>
       </c>
       <c r="B36" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>129373230</v>
       </c>
       <c r="B37" t="n">
-        <v>75182</v>
+        <v>75187</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>129373216</v>
       </c>
       <c r="B38" t="n">
-        <v>78473</v>
+        <v>78478</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>129373273</v>
       </c>
       <c r="B39" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>129373119</v>
       </c>
       <c r="B41" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129425231</v>
+        <v>129425498</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>79694</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4912,43 +4912,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4956,13 +4939,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557727</v>
+        <v>557870</v>
       </c>
       <c r="R43" t="n">
-        <v>6461009</v>
+        <v>6461347</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4994,17 +4977,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5023,10 +5002,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129425498</v>
+        <v>129425231</v>
       </c>
       <c r="B44" t="n">
-        <v>79689</v>
+        <v>57732</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5034,26 +5013,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5061,13 +5057,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557870</v>
+        <v>557727</v>
       </c>
       <c r="R44" t="n">
-        <v>6461347</v>
+        <v>6461009</v>
       </c>
       <c r="S44" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5099,13 +5095,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>129425486</v>
       </c>
       <c r="B45" t="n">
-        <v>92234</v>
+        <v>92240</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>129425154</v>
       </c>
       <c r="B46" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1564,6 +1564,15 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Herrsätter Strålången, Ög</t>
@@ -2340,6 +2349,14 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Herrsätter Strålången, Ög</t>
@@ -2631,6 +2648,15 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Herrsätter Strålången, Ög</t>
@@ -2681,6 +2707,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2702,7 +2729,7 @@
         <v>129372672</v>
       </c>
       <c r="B22" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,7 +2839,7 @@
         <v>129373539</v>
       </c>
       <c r="B23" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2944,7 @@
         <v>129373239</v>
       </c>
       <c r="B24" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3022,7 +3049,7 @@
         <v>129373315</v>
       </c>
       <c r="B25" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3140,7 +3167,7 @@
         <v>129373370</v>
       </c>
       <c r="B26" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3245,7 +3272,7 @@
         <v>129373250</v>
       </c>
       <c r="B27" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3343,10 +3370,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129373253</v>
+        <v>129372647</v>
       </c>
       <c r="B28" t="n">
-        <v>81060</v>
+        <v>79695</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,21 +3381,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3408,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557837</v>
+        <v>557761</v>
       </c>
       <c r="R28" t="n">
-        <v>6461265</v>
+        <v>6460898</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,10 +3471,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129372647</v>
+        <v>129373253</v>
       </c>
       <c r="B29" t="n">
-        <v>79694</v>
+        <v>81061</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3455,21 +3482,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3482,10 +3509,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557761</v>
+        <v>557837</v>
       </c>
       <c r="R29" t="n">
-        <v>6460898</v>
+        <v>6461265</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3548,7 +3575,7 @@
         <v>129373262</v>
       </c>
       <c r="B30" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3649,7 +3676,7 @@
         <v>129373243</v>
       </c>
       <c r="B31" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3777,7 @@
         <v>129373551</v>
       </c>
       <c r="B32" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3851,7 +3878,7 @@
         <v>129373521</v>
       </c>
       <c r="B33" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3956,7 +3983,7 @@
         <v>129373557</v>
       </c>
       <c r="B34" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4057,7 +4084,7 @@
         <v>129373573</v>
       </c>
       <c r="B35" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4179,7 +4206,7 @@
         <v>129373529</v>
       </c>
       <c r="B36" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4284,7 +4311,7 @@
         <v>129373230</v>
       </c>
       <c r="B37" t="n">
-        <v>75187</v>
+        <v>75188</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4382,10 +4409,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129373216</v>
+        <v>129373273</v>
       </c>
       <c r="B38" t="n">
-        <v>78478</v>
+        <v>92908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,24 +4420,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4420,10 +4451,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557861</v>
+        <v>557842</v>
       </c>
       <c r="R38" t="n">
-        <v>6461205</v>
+        <v>6461313</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,11 +4487,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4488,10 +4514,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129373273</v>
+        <v>129373216</v>
       </c>
       <c r="B39" t="n">
-        <v>92907</v>
+        <v>78479</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4499,28 +4525,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4530,10 +4552,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557842</v>
+        <v>557861</v>
       </c>
       <c r="R39" t="n">
-        <v>6461313</v>
+        <v>6461205</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,6 +4588,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4699,7 +4726,7 @@
         <v>129373119</v>
       </c>
       <c r="B41" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4901,10 +4928,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129425498</v>
+        <v>129425231</v>
       </c>
       <c r="B43" t="n">
-        <v>79694</v>
+        <v>57733</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4912,26 +4939,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4939,13 +4983,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557870</v>
+        <v>557727</v>
       </c>
       <c r="R43" t="n">
-        <v>6461347</v>
+        <v>6461009</v>
       </c>
       <c r="S43" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4977,13 +5021,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5002,10 +5050,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129425231</v>
+        <v>129425498</v>
       </c>
       <c r="B44" t="n">
-        <v>57732</v>
+        <v>79695</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5013,43 +5061,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5057,13 +5088,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557727</v>
+        <v>557870</v>
       </c>
       <c r="R44" t="n">
-        <v>6461009</v>
+        <v>6461347</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5095,17 +5126,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5127,7 +5154,7 @@
         <v>129425486</v>
       </c>
       <c r="B45" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5232,7 +5259,7 @@
         <v>129425154</v>
       </c>
       <c r="B46" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -3164,10 +3164,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129373370</v>
+        <v>129373250</v>
       </c>
       <c r="B26" t="n">
-        <v>92908</v>
+        <v>79695</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3175,28 +3175,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3206,10 +3202,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557786</v>
+        <v>557837</v>
       </c>
       <c r="R26" t="n">
-        <v>6461383</v>
+        <v>6461265</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3269,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129373250</v>
+        <v>129373370</v>
       </c>
       <c r="B27" t="n">
-        <v>79695</v>
+        <v>92908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3280,24 +3276,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557837</v>
+        <v>557786</v>
       </c>
       <c r="R27" t="n">
-        <v>6461265</v>
+        <v>6461383</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4928,10 +4928,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129425231</v>
+        <v>129425498</v>
       </c>
       <c r="B43" t="n">
-        <v>57733</v>
+        <v>79695</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4939,43 +4939,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4983,13 +4966,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557727</v>
+        <v>557870</v>
       </c>
       <c r="R43" t="n">
-        <v>6461009</v>
+        <v>6461347</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5021,17 +5004,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5050,10 +5029,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129425498</v>
+        <v>129425231</v>
       </c>
       <c r="B44" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5061,26 +5040,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5088,13 +5084,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557870</v>
+        <v>557727</v>
       </c>
       <c r="R44" t="n">
-        <v>6461347</v>
+        <v>6461009</v>
       </c>
       <c r="S44" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5126,13 +5122,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2839,7 +2839,7 @@
         <v>129373539</v>
       </c>
       <c r="B23" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129373250</v>
+        <v>129373370</v>
       </c>
       <c r="B26" t="n">
-        <v>79695</v>
+        <v>92913</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3175,24 +3175,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3202,10 +3206,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557837</v>
+        <v>557786</v>
       </c>
       <c r="R26" t="n">
-        <v>6461265</v>
+        <v>6461383</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3265,10 +3269,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129373370</v>
+        <v>129373250</v>
       </c>
       <c r="B27" t="n">
-        <v>92908</v>
+        <v>79700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3276,28 +3280,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557786</v>
+        <v>557837</v>
       </c>
       <c r="R27" t="n">
-        <v>6461383</v>
+        <v>6461265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129372647</v>
+        <v>129373253</v>
       </c>
       <c r="B28" t="n">
-        <v>79695</v>
+        <v>81066</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,21 +3381,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557761</v>
+        <v>557837</v>
       </c>
       <c r="R28" t="n">
-        <v>6460898</v>
+        <v>6461265</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129373253</v>
+        <v>129372647</v>
       </c>
       <c r="B29" t="n">
-        <v>81061</v>
+        <v>79700</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3482,21 +3482,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557837</v>
+        <v>557761</v>
       </c>
       <c r="R29" t="n">
-        <v>6461265</v>
+        <v>6460898</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3575,7 +3575,7 @@
         <v>129373262</v>
       </c>
       <c r="B30" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>129373243</v>
       </c>
       <c r="B31" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>129373551</v>
       </c>
       <c r="B32" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>129373521</v>
       </c>
       <c r="B33" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>129373557</v>
       </c>
       <c r="B34" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4203,39 +4203,35 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129373529</v>
+        <v>129373230</v>
       </c>
       <c r="B36" t="n">
-        <v>92908</v>
+        <v>75193</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4245,10 +4241,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557783</v>
+        <v>557888</v>
       </c>
       <c r="R36" t="n">
-        <v>6461366</v>
+        <v>6461234</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4308,35 +4304,39 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129373230</v>
+        <v>129373529</v>
       </c>
       <c r="B37" t="n">
-        <v>75188</v>
+        <v>92913</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557888</v>
+        <v>557783</v>
       </c>
       <c r="R37" t="n">
-        <v>6461234</v>
+        <v>6461366</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4412,7 +4412,7 @@
         <v>129373273</v>
       </c>
       <c r="B38" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>129373216</v>
       </c>
       <c r="B39" t="n">
-        <v>78479</v>
+        <v>78484</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>129373119</v>
       </c>
       <c r="B41" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4928,10 +4928,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129425498</v>
+        <v>129425231</v>
       </c>
       <c r="B43" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4939,26 +4939,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4966,13 +4983,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557870</v>
+        <v>557727</v>
       </c>
       <c r="R43" t="n">
-        <v>6461347</v>
+        <v>6461009</v>
       </c>
       <c r="S43" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5004,13 +5021,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5029,10 +5050,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129425231</v>
+        <v>129425498</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5040,43 +5061,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5084,13 +5088,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557727</v>
+        <v>557870</v>
       </c>
       <c r="R44" t="n">
-        <v>6461009</v>
+        <v>6461347</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5122,17 +5126,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>129425486</v>
       </c>
       <c r="B45" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>129425154</v>
       </c>
       <c r="B46" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Sofie Karlsson</t>
+          <t>Sofie Karlsson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129373370</v>
+        <v>129373250</v>
       </c>
       <c r="B26" t="n">
-        <v>92913</v>
+        <v>79700</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3175,28 +3175,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3206,10 +3202,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557786</v>
+        <v>557837</v>
       </c>
       <c r="R26" t="n">
-        <v>6461383</v>
+        <v>6461265</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3269,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129373250</v>
+        <v>129373370</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>92913</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3280,24 +3276,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557837</v>
+        <v>557786</v>
       </c>
       <c r="R27" t="n">
-        <v>6461265</v>
+        <v>6461383</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129373253</v>
+        <v>129372647</v>
       </c>
       <c r="B28" t="n">
-        <v>81066</v>
+        <v>79700</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,21 +3381,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557837</v>
+        <v>557761</v>
       </c>
       <c r="R28" t="n">
-        <v>6461265</v>
+        <v>6460898</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129372647</v>
+        <v>129373253</v>
       </c>
       <c r="B29" t="n">
-        <v>79700</v>
+        <v>81066</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3482,21 +3482,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557761</v>
+        <v>557837</v>
       </c>
       <c r="R29" t="n">
-        <v>6460898</v>
+        <v>6461265</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4203,35 +4203,39 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129373230</v>
+        <v>129373529</v>
       </c>
       <c r="B36" t="n">
-        <v>75193</v>
+        <v>92913</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4241,10 +4245,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557888</v>
+        <v>557783</v>
       </c>
       <c r="R36" t="n">
-        <v>6461234</v>
+        <v>6461366</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4304,39 +4308,35 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129373529</v>
+        <v>129373230</v>
       </c>
       <c r="B37" t="n">
-        <v>92913</v>
+        <v>75193</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557783</v>
+        <v>557888</v>
       </c>
       <c r="R37" t="n">
-        <v>6461366</v>
+        <v>6461234</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4409,10 +4409,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129373273</v>
+        <v>129373216</v>
       </c>
       <c r="B38" t="n">
-        <v>92913</v>
+        <v>78484</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4420,28 +4420,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4451,10 +4447,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557842</v>
+        <v>557861</v>
       </c>
       <c r="R38" t="n">
-        <v>6461313</v>
+        <v>6461205</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4487,6 +4483,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4514,10 +4515,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129373216</v>
+        <v>129373273</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
+        <v>92913</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4525,24 +4526,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4552,10 +4557,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557861</v>
+        <v>557842</v>
       </c>
       <c r="R39" t="n">
-        <v>6461205</v>
+        <v>6461313</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4588,11 +4593,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4928,10 +4928,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129425231</v>
+        <v>129425498</v>
       </c>
       <c r="B43" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4939,43 +4939,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4983,13 +4966,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557727</v>
+        <v>557870</v>
       </c>
       <c r="R43" t="n">
-        <v>6461009</v>
+        <v>6461347</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5021,17 +5004,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5050,10 +5029,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129425498</v>
+        <v>129425231</v>
       </c>
       <c r="B44" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5061,26 +5040,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5088,13 +5084,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557870</v>
+        <v>557727</v>
       </c>
       <c r="R44" t="n">
-        <v>6461347</v>
+        <v>6461009</v>
       </c>
       <c r="S44" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5126,13 +5122,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sofie Karlsson, Marika Sjödin</t>
+          <t>Marika Sjödin, Sofie Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129372647</v>
+        <v>129373253</v>
       </c>
       <c r="B28" t="n">
-        <v>79700</v>
+        <v>81066</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,21 +3381,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557761</v>
+        <v>557837</v>
       </c>
       <c r="R28" t="n">
-        <v>6460898</v>
+        <v>6461265</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129373253</v>
+        <v>129372647</v>
       </c>
       <c r="B29" t="n">
-        <v>81066</v>
+        <v>79700</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3482,21 +3482,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557837</v>
+        <v>557761</v>
       </c>
       <c r="R29" t="n">
-        <v>6461265</v>
+        <v>6460898</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4203,39 +4203,35 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129373529</v>
+        <v>129373230</v>
       </c>
       <c r="B36" t="n">
-        <v>92913</v>
+        <v>75193</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4245,10 +4241,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557783</v>
+        <v>557888</v>
       </c>
       <c r="R36" t="n">
-        <v>6461366</v>
+        <v>6461234</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4308,35 +4304,39 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129373230</v>
+        <v>129373529</v>
       </c>
       <c r="B37" t="n">
-        <v>75193</v>
+        <v>92913</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557888</v>
+        <v>557783</v>
       </c>
       <c r="R37" t="n">
-        <v>6461234</v>
+        <v>6461366</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4928,10 +4928,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129425498</v>
+        <v>129425231</v>
       </c>
       <c r="B43" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4939,26 +4939,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4966,13 +4983,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557870</v>
+        <v>557727</v>
       </c>
       <c r="R43" t="n">
-        <v>6461347</v>
+        <v>6461009</v>
       </c>
       <c r="S43" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5004,13 +5021,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5029,10 +5050,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129425231</v>
+        <v>129425498</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5040,43 +5061,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5084,13 +5088,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557727</v>
+        <v>557870</v>
       </c>
       <c r="R44" t="n">
-        <v>6461009</v>
+        <v>6461347</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5122,17 +5126,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -3164,10 +3164,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129373250</v>
+        <v>129373370</v>
       </c>
       <c r="B26" t="n">
-        <v>79700</v>
+        <v>92913</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3175,24 +3175,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3202,10 +3206,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557837</v>
+        <v>557786</v>
       </c>
       <c r="R26" t="n">
-        <v>6461265</v>
+        <v>6461383</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3265,10 +3269,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129373370</v>
+        <v>129373250</v>
       </c>
       <c r="B27" t="n">
-        <v>92913</v>
+        <v>79700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3276,28 +3280,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557786</v>
+        <v>557837</v>
       </c>
       <c r="R27" t="n">
-        <v>6461383</v>
+        <v>6461265</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4409,10 +4409,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129373216</v>
+        <v>129373273</v>
       </c>
       <c r="B38" t="n">
-        <v>78484</v>
+        <v>92913</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4420,24 +4420,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4447,10 +4451,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557861</v>
+        <v>557842</v>
       </c>
       <c r="R38" t="n">
-        <v>6461205</v>
+        <v>6461313</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4483,11 +4487,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4515,10 +4514,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129373273</v>
+        <v>129373216</v>
       </c>
       <c r="B39" t="n">
-        <v>92913</v>
+        <v>78484</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4526,28 +4525,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4557,10 +4552,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557842</v>
+        <v>557861</v>
       </c>
       <c r="R39" t="n">
-        <v>6461313</v>
+        <v>6461205</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4593,6 +4588,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4928,10 +4928,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129425231</v>
+        <v>129425498</v>
       </c>
       <c r="B43" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4939,43 +4939,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4983,13 +4966,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557727</v>
+        <v>557870</v>
       </c>
       <c r="R43" t="n">
-        <v>6461009</v>
+        <v>6461347</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5021,17 +5004,13 @@
           <t>2025-10-29</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5050,10 +5029,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129425498</v>
+        <v>129425231</v>
       </c>
       <c r="B44" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5061,26 +5040,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5088,13 +5084,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557870</v>
+        <v>557727</v>
       </c>
       <c r="R44" t="n">
-        <v>6461347</v>
+        <v>6461009</v>
       </c>
       <c r="S44" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5126,13 +5122,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -5154,7 +5154,7 @@
         <v>129425486</v>
       </c>
       <c r="B45" t="n">
-        <v>92246</v>
+        <v>92250</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>129425154</v>
       </c>
       <c r="B46" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4928,38 +4928,39 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129425498</v>
+        <v>129874752</v>
       </c>
       <c r="B43" t="n">
-        <v>79700</v>
+        <v>98780</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Herrsätter, Ög</t>
@@ -4969,10 +4970,10 @@
         <v>557870</v>
       </c>
       <c r="R43" t="n">
-        <v>6461347</v>
+        <v>6461372</v>
       </c>
       <c r="S43" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4994,6 +4995,11 @@
           <t>Värna</t>
         </is>
       </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>E-Åtv-0281</t>
+        </is>
+      </c>
       <c r="Y43" t="inlineStr">
         <is>
           <t>2025-10-29</t>
@@ -5004,28 +5010,36 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Enstaka dvs. två plantor noterades.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
           <t>Steve Daurer</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5151,39 +5165,35 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129425486</v>
+        <v>129425498</v>
       </c>
       <c r="B45" t="n">
-        <v>92250</v>
+        <v>79700</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6031</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5193,10 +5203,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557860</v>
+        <v>557870</v>
       </c>
       <c r="R45" t="n">
-        <v>6461363</v>
+        <v>6461347</v>
       </c>
       <c r="S45" t="n">
         <v>100</v>
@@ -5256,35 +5266,39 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129425154</v>
+        <v>129425486</v>
       </c>
       <c r="B46" t="n">
-        <v>91597</v>
+        <v>92252</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5294,13 +5308,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557727</v>
+        <v>557860</v>
       </c>
       <c r="R46" t="n">
-        <v>6460998</v>
+        <v>6461363</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5354,6 +5368,107 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129425154</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91599</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Herrsätter, Ög</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>557727</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6460998</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4931,7 +4931,7 @@
         <v>129874752</v>
       </c>
       <c r="B43" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4931,7 +4931,7 @@
         <v>129874752</v>
       </c>
       <c r="B43" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -1538,7 +1538,7 @@
         <v>127399707</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>127399713</v>
       </c>
       <c r="B21" t="n">
-        <v>8439</v>
+        <v>8440</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>129874752</v>
       </c>
       <c r="B43" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4931,7 +4931,7 @@
         <v>129874752</v>
       </c>
       <c r="B43" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4931,7 +4931,7 @@
         <v>129874752</v>
       </c>
       <c r="B43" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4931,7 +4931,7 @@
         <v>129874752</v>
       </c>
       <c r="B43" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4931,7 +4931,7 @@
         <v>129874752</v>
       </c>
       <c r="B43" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4931,7 +4931,7 @@
         <v>129874752</v>
       </c>
       <c r="B43" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4084,7 +4084,7 @@
         <v>129373573</v>
       </c>
       <c r="B35" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4084,7 +4084,7 @@
         <v>129373573</v>
       </c>
       <c r="B35" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4084,7 +4084,7 @@
         <v>129373573</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4084,7 +4084,7 @@
         <v>129373573</v>
       </c>
       <c r="B35" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4084,7 +4084,7 @@
         <v>129373573</v>
       </c>
       <c r="B35" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4084,7 +4084,7 @@
         <v>129373573</v>
       </c>
       <c r="B35" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4084,7 +4084,7 @@
         <v>129373573</v>
       </c>
       <c r="B35" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4084,7 +4084,7 @@
         <v>129373573</v>
       </c>
       <c r="B35" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -4084,7 +4084,7 @@
         <v>129373573</v>
       </c>
       <c r="B35" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55710761</v>
+        <v>127399687</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjöbacka, 250m S., Ög</t>
+          <t>Herrsätter Strålången, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557858.0552695113</v>
+        <v>557958</v>
       </c>
       <c r="R2" t="n">
-        <v>6461006.107662208</v>
+        <v>6461315</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-08-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-08-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,84 +754,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>tre gamla tallar</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kjell Mathson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kjell Mathson</t>
+          <t>Marika Sjödin, Sofie Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55710708</v>
+        <v>129373119</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Herrsätter, 650m O., Ög</t>
+          <t>Herrsäter, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557853.2545516044</v>
+        <v>557870</v>
       </c>
       <c r="R3" t="n">
-        <v>6461405.656757139</v>
+        <v>6461202</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2000-05-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-05-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,40 +859,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>bergbrant</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>gammal tall</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kjell Mathson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kjell Mathson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55710655</v>
+        <v>129373253</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,39 +885,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Herrsätter, 600m O., Ög</t>
+          <t>Herrsäter, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557853.2545516044</v>
+        <v>557837</v>
       </c>
       <c r="R4" t="n">
-        <v>6461405.656757139</v>
+        <v>6461265</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2000-05-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2000-05-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,73 +960,65 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kjell Mathson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kjell Mathson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127399720</v>
+        <v>55710655</v>
       </c>
       <c r="B5" t="n">
-        <v>95822</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Herrsätter Strålången, Ög</t>
+          <t>Herrsätter, 600m O., Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557888</v>
+        <v>557853</v>
       </c>
       <c r="R5" t="n">
-        <v>6461208</v>
+        <v>6461406</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,12 +1042,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2000-05-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2000-05-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,66 +1056,80 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Kjell Mathson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Sofie Karlsson</t>
+          <t>Kjell Mathson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127399725</v>
+        <v>129425154</v>
       </c>
       <c r="B6" t="n">
-        <v>95822</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Herrsätter Strålången, Ög</t>
+          <t>Herrsätter, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557881</v>
+        <v>557727</v>
       </c>
       <c r="R6" t="n">
-        <v>6461180</v>
+        <v>6460998</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,50 +1167,51 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Sofie Karlsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127399709</v>
+        <v>127399715</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>96601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557828</v>
+        <v>557855</v>
       </c>
       <c r="R7" t="n">
-        <v>6461278</v>
+        <v>6461214</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1341,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127399721</v>
+        <v>127399716</v>
       </c>
       <c r="B8" t="n">
-        <v>95822</v>
+        <v>96601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,21 +1294,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557884</v>
+        <v>557860</v>
       </c>
       <c r="R8" t="n">
-        <v>6461188</v>
+        <v>6461212</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1438,32 +1380,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127399712</v>
+        <v>127399718</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>96601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557855</v>
+        <v>557887</v>
       </c>
       <c r="R9" t="n">
-        <v>6461214</v>
+        <v>6461210</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1535,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127399707</v>
+        <v>127399723</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>96601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,43 +1488,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Herrsätter Strålången, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557879</v>
+        <v>557874</v>
       </c>
       <c r="R10" t="n">
-        <v>6461294</v>
+        <v>6461193</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1641,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127399728</v>
+        <v>127399726</v>
       </c>
       <c r="B11" t="n">
-        <v>100652</v>
+        <v>96708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,21 +1585,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557906</v>
+        <v>557876</v>
       </c>
       <c r="R11" t="n">
-        <v>6460932</v>
+        <v>6461182</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1738,10 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127399727</v>
+        <v>127399717</v>
       </c>
       <c r="B12" t="n">
-        <v>100652</v>
+        <v>96458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,21 +1682,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557937</v>
+        <v>557863</v>
       </c>
       <c r="R12" t="n">
-        <v>6460931</v>
+        <v>6461210</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1835,32 +1768,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127399710</v>
+        <v>127399720</v>
       </c>
       <c r="B13" t="n">
-        <v>79647</v>
+        <v>96458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1870,10 +1803,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557834</v>
+        <v>557888</v>
       </c>
       <c r="R13" t="n">
-        <v>6461267</v>
+        <v>6461208</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1932,10 +1865,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127399715</v>
+        <v>127399721</v>
       </c>
       <c r="B14" t="n">
-        <v>95965</v>
+        <v>96458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,21 +1876,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1900,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557855</v>
+        <v>557884</v>
       </c>
       <c r="R14" t="n">
-        <v>6461214</v>
+        <v>6461188</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2029,10 +1962,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127399717</v>
+        <v>127399725</v>
       </c>
       <c r="B15" t="n">
-        <v>95822</v>
+        <v>96458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,10 +1997,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557863</v>
+        <v>557881</v>
       </c>
       <c r="R15" t="n">
-        <v>6461210</v>
+        <v>6461180</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2126,48 +2059,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127399716</v>
+        <v>55710708</v>
       </c>
       <c r="B16" t="n">
-        <v>95965</v>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Herrsätter Strålången, Ög</t>
+          <t>Herrsätter, 650m O., Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557860</v>
+        <v>557853</v>
       </c>
       <c r="R16" t="n">
-        <v>6461212</v>
+        <v>6461406</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2191,12 +2126,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2000-05-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2000-05-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,66 +2140,79 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>bergbrant</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>gammal tall</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Kjell Mathson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Sofie Karlsson</t>
+          <t>Kjell Mathson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127399723</v>
+        <v>55710761</v>
       </c>
       <c r="B17" t="n">
-        <v>95965</v>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Herrsätter Strålången, Ög</t>
+          <t>Sjöbacka, 250m S., Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557874</v>
+        <v>557858</v>
       </c>
       <c r="R17" t="n">
-        <v>6461193</v>
+        <v>6461006</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2288,12 +2236,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2000-08-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2000-08-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2302,71 +2250,74 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>tre gamla tallar</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Kjell Mathson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Sofie Karlsson</t>
+          <t>Kjell Mathson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127399708</v>
+        <v>127399701</v>
       </c>
       <c r="B18" t="n">
-        <v>4986</v>
+        <v>91930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100307</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Herrsätter Strålången, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557825</v>
+        <v>557937</v>
       </c>
       <c r="R18" t="n">
-        <v>6461277</v>
+        <v>6461309</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2425,10 +2376,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127399706</v>
+        <v>127399703</v>
       </c>
       <c r="B19" t="n">
-        <v>78787</v>
+        <v>91930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,21 +2387,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2460,7 +2411,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557932</v>
+        <v>557950</v>
       </c>
       <c r="R19" t="n">
         <v>6461352</v>
@@ -2522,32 +2473,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127399718</v>
+        <v>127399704</v>
       </c>
       <c r="B20" t="n">
-        <v>95965</v>
+        <v>91930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2557,10 +2508,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557887</v>
+        <v>557947</v>
       </c>
       <c r="R20" t="n">
-        <v>6461210</v>
+        <v>6461351</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2619,57 +2570,55 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127399713</v>
+        <v>129373273</v>
       </c>
       <c r="B21" t="n">
-        <v>8440</v>
+        <v>93235</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Herrsätter Strålången, Ög</t>
+          <t>Herrsäter, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557855</v>
+        <v>557842</v>
       </c>
       <c r="R21" t="n">
-        <v>6461214</v>
+        <v>6461313</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2693,12 +2642,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2714,22 +2663,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Sofie Karlsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129372672</v>
+        <v>129373370</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2737,31 +2686,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2769,10 +2717,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557761</v>
+        <v>557786</v>
       </c>
       <c r="R22" t="n">
-        <v>6460898</v>
+        <v>6461383</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,17 +2755,13 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>färska och äldre hack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2836,10 +2780,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129373539</v>
+        <v>129373521</v>
       </c>
       <c r="B23" t="n">
-        <v>92913</v>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2866,7 +2810,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -2878,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557822</v>
+        <v>557768</v>
       </c>
       <c r="R23" t="n">
-        <v>6461312</v>
+        <v>6461405</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,10 +2885,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129373239</v>
+        <v>129373529</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,31 +2896,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2984,10 +2927,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557888</v>
+        <v>557783</v>
       </c>
       <c r="R24" t="n">
-        <v>6461234</v>
+        <v>6461366</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3028,6 +2971,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3046,10 +2990,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129373315</v>
+        <v>129373539</v>
       </c>
       <c r="B25" t="n">
-        <v>57896</v>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3057,21 +3001,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3079,17 +3023,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3097,10 +3032,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557831</v>
+        <v>557822</v>
       </c>
       <c r="R25" t="n">
-        <v>6461322</v>
+        <v>6461312</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3135,17 +3070,13 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Revirparet i sitt permanenta revir respektive i viktig del av reviret.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3164,39 +3095,35 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129373370</v>
+        <v>129373262</v>
       </c>
       <c r="B26" t="n">
-        <v>92913</v>
+        <v>92567</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3206,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557786</v>
+        <v>557835</v>
       </c>
       <c r="R26" t="n">
-        <v>6461383</v>
+        <v>6461268</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3269,51 +3196,55 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129373250</v>
+        <v>129425486</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>92567</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Herrsäter, Ög</t>
+          <t>Herrsätter, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557837</v>
+        <v>557860</v>
       </c>
       <c r="R27" t="n">
-        <v>6461265</v>
+        <v>6461363</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3337,12 +3268,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3370,10 +3301,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129373253</v>
+        <v>129373230</v>
       </c>
       <c r="B28" t="n">
-        <v>81066</v>
+        <v>75428</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,21 +3312,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3408,10 +3339,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557837</v>
+        <v>557888</v>
       </c>
       <c r="R28" t="n">
-        <v>6461265</v>
+        <v>6461234</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3471,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129372647</v>
+        <v>129373216</v>
       </c>
       <c r="B29" t="n">
-        <v>79700</v>
+        <v>78730</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3482,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3509,10 +3440,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557761</v>
+        <v>557861</v>
       </c>
       <c r="R29" t="n">
-        <v>6460898</v>
+        <v>6461205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,6 +3476,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3572,51 +3508,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129373262</v>
+        <v>127399706</v>
       </c>
       <c r="B30" t="n">
-        <v>92246</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6031</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Herrsäter, Ög</t>
+          <t>Herrsätter Strålången, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557835</v>
+        <v>557932</v>
       </c>
       <c r="R30" t="n">
-        <v>6461268</v>
+        <v>6461352</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3640,12 +3573,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3654,29 +3587,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Marika Sjödin, Sofie Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129373243</v>
+        <v>127399682</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3702,22 +3634,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Herrsäter, Ög</t>
+          <t>Herrsätter Strålången, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557858</v>
+        <v>557678</v>
       </c>
       <c r="R31" t="n">
-        <v>6461263</v>
+        <v>6461003</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3741,12 +3670,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3755,29 +3684,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Marika Sjödin, Sofie Karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129373551</v>
+        <v>127399709</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3803,22 +3731,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Herrsäter, Ög</t>
+          <t>Herrsätter Strålången, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557913</v>
+        <v>557828</v>
       </c>
       <c r="R32" t="n">
-        <v>6461341</v>
+        <v>6461278</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3842,12 +3767,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3856,29 +3781,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Marika Sjödin, Sofie Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129373521</v>
+        <v>127399710</v>
       </c>
       <c r="B33" t="n">
-        <v>92913</v>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3886,44 +3810,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Herrsäter, Ög</t>
+          <t>Herrsätter Strålången, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557768</v>
+        <v>557834</v>
       </c>
       <c r="R33" t="n">
-        <v>6461405</v>
+        <v>6461267</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3947,12 +3864,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3961,29 +3878,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Marika Sjödin, Sofie Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129373557</v>
+        <v>129372647</v>
       </c>
       <c r="B34" t="n">
-        <v>79700</v>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4018,10 +3934,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557914</v>
+        <v>557761</v>
       </c>
       <c r="R34" t="n">
-        <v>6461343</v>
+        <v>6460898</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4081,10 +3997,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129373573</v>
+        <v>129373243</v>
       </c>
       <c r="B35" t="n">
-        <v>57901</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4092,43 +4008,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4136,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557883</v>
+        <v>557858</v>
       </c>
       <c r="R35" t="n">
-        <v>6461355</v>
+        <v>6461263</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4174,17 +4073,13 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hane i sitt permanenta revir hackandes på en äldre asplåga.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4203,32 +4098,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129373230</v>
+        <v>129373250</v>
       </c>
       <c r="B36" t="n">
-        <v>75193</v>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4241,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557888</v>
+        <v>557837</v>
       </c>
       <c r="R36" t="n">
-        <v>6461234</v>
+        <v>6461265</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4304,10 +4199,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129373529</v>
+        <v>129373551</v>
       </c>
       <c r="B37" t="n">
-        <v>92913</v>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4315,28 +4210,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4346,10 +4237,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557783</v>
+        <v>557913</v>
       </c>
       <c r="R37" t="n">
-        <v>6461366</v>
+        <v>6461341</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4409,10 +4300,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129373273</v>
+        <v>129373557</v>
       </c>
       <c r="B38" t="n">
-        <v>92913</v>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4420,28 +4311,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4451,10 +4338,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557842</v>
+        <v>557914</v>
       </c>
       <c r="R38" t="n">
-        <v>6461313</v>
+        <v>6461343</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4514,10 +4401,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129373216</v>
+        <v>129425498</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4525,21 +4412,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4548,17 +4435,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Herrsäter, Ög</t>
+          <t>Herrsätter, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557861</v>
+        <v>557870</v>
       </c>
       <c r="R39" t="n">
-        <v>6461205</v>
+        <v>6461347</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4582,17 +4469,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka fruktkroppar bland en massa andra mörka spiklavar.</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4620,53 +4502,64 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129373098</v>
+        <v>127104735</v>
       </c>
       <c r="B40" t="n">
-        <v>5177</v>
+        <v>57966</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>100048</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Herrsäter, Ög</t>
+          <t>Herrsätter/Strålången, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557884</v>
+        <v>557933</v>
       </c>
       <c r="R40" t="n">
-        <v>6461195</v>
+        <v>6461232</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4690,12 +4583,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4704,57 +4597,72 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Rebecka  Hovenberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Rebecka  Hovenberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129373119</v>
+        <v>129373183</v>
       </c>
       <c r="B41" t="n">
-        <v>96216</v>
+        <v>57966</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>210</v>
+        <v>100048</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4762,10 +4670,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557870</v>
+        <v>557855</v>
       </c>
       <c r="R41" t="n">
-        <v>6461202</v>
+        <v>6461178</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4800,13 +4708,17 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Sumpskogen och den omgivande skogen utgör en viktig del av mindre hackspettens revir</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4825,10 +4737,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129425252</v>
+        <v>127105209</v>
       </c>
       <c r="B42" t="n">
-        <v>4773</v>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4836,42 +4748,53 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Herrsätter, Ög</t>
+          <t>Herrsätter/Strålången, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557720</v>
+        <v>557923</v>
       </c>
       <c r="R42" t="n">
-        <v>6461009</v>
+        <v>6461242</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4895,12 +4818,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4909,71 +4832,66 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Rebecka  Hovenberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Rebecka  Hovenberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129874752</v>
+        <v>127399712</v>
       </c>
       <c r="B43" t="n">
-        <v>98833</v>
+        <v>57950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Herrsätter, Ög</t>
+          <t>Herrsätter Strålången, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557870</v>
+        <v>557855</v>
       </c>
       <c r="R43" t="n">
-        <v>6461372</v>
+        <v>6461214</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4995,24 +4913,14 @@
           <t>Värna</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>E-Åtv-0281</t>
-        </is>
-      </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Enstaka dvs. två plantor noterades.</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5027,30 +4935,26 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129425231</v>
+        <v>129372672</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5071,37 +4975,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Herrsätter, Ög</t>
+          <t>Herrsäter, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557727</v>
+        <v>557761</v>
       </c>
       <c r="R44" t="n">
-        <v>6461009</v>
+        <v>6460898</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5128,17 +5020,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
+          <t>färska och äldre hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5165,51 +5057,56 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129425498</v>
+        <v>129373239</v>
       </c>
       <c r="B45" t="n">
-        <v>79700</v>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Herrsätter, Ög</t>
+          <t>Herrsäter, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557870</v>
+        <v>557888</v>
       </c>
       <c r="R45" t="n">
-        <v>6461347</v>
+        <v>6461234</v>
       </c>
       <c r="S45" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5233,12 +5130,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5247,7 +5144,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5266,10 +5162,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129425486</v>
+        <v>129373573</v>
       </c>
       <c r="B46" t="n">
-        <v>92252</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5277,21 +5173,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6031</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5299,22 +5195,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Herrsätter, Ög</t>
+          <t>Herrsäter, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557860</v>
+        <v>557883</v>
       </c>
       <c r="R46" t="n">
-        <v>6461363</v>
+        <v>6461355</v>
       </c>
       <c r="S46" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5338,12 +5247,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hane i sitt permanenta revir hackandes på en äldre asplåga.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5352,7 +5266,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5371,37 +5284,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129425154</v>
+        <v>129425231</v>
       </c>
       <c r="B47" t="n">
-        <v>91599</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5412,7 +5342,7 @@
         <v>557727</v>
       </c>
       <c r="R47" t="n">
-        <v>6460998</v>
+        <v>6461009</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5447,13 +5377,17 @@
           <t>2025-10-29</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Man förstår att mängden på granlågorna på platsen efter barkborrens angrepp och även rötlågågor efter ca 80 till 100 årig gran är rena matbordet åt spillkråkan. Intressant också att på samma plats har det hittats den rödlistade tickan ullticka, vilket som ger bevis på att granarna var ej planterade utan självsådda under ett naturligt överbestånd och således rest av kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5469,6 +5403,1387 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127399702</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>557947</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6461360</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129425252</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Herrsätter, Ög</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>557720</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6461009</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127399708</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4988</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100307</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blompraktbagge</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Anthaxia morio</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>557825</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6461277</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129373098</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>557884</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6461195</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127399684</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>557943</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6461243</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129373315</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Herrsäter, Ög</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>557831</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6461322</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Revirparet i sitt permanenta revir respektive i viktig del av reviret.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127399707</v>
+      </c>
+      <c r="B54" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>557879</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6461294</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127399713</v>
+      </c>
+      <c r="B55" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>557855</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6461214</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128053525</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Herrsätter/Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>557835</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6461208</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Något osäker artbestämning, kan ha varit åkergroda.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Rebecka  Hovenberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Rebecka  Hovenberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127399685</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>557955</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6461312</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129874752</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Herrsätter, Ög</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>557870</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6461372</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>E-Åtv-0281</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Enstaka dvs. två plantor noterades.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127399727</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>557937</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6460931</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127399728</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Herrsätter Strålången, Ög</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>557906</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6460932</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Värna</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Sofie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22257-2025 artfynd.xlsx
+++ b/artfynd/A 22257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399682</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399687</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373119</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373253</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55710655</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425154</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1377,6 +1412,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399715</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1474,6 +1514,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399716</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,6 +1616,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399718</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1668,6 +1718,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399723</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1765,6 +1820,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399726</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1862,6 +1922,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399717</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1959,6 +2024,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399720</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2056,6 +2126,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399721</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2153,6 +2228,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399725</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2263,6 +2343,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55710708</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2373,6 +2458,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55710761</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2470,6 +2560,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399701</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2567,6 +2662,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399703</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2664,6 +2764,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399704</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2769,6 +2874,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373273</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2874,6 +2984,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373370</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2979,6 +3094,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373521</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3084,6 +3204,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373529</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3189,6 +3314,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373539</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3290,6 +3420,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373262</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3395,6 +3530,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425486</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3496,6 +3636,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373230</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3602,6 +3747,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373216</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3699,6 +3849,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399706</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3796,6 +3951,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399709</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3893,6 +4053,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399710</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3994,6 +4159,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372647</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4095,6 +4265,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373243</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4196,6 +4371,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373250</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4297,6 +4477,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373551</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4398,6 +4583,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373557</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4499,6 +4689,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425498</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4612,6 +4807,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127104735</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4734,6 +4934,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373183</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4847,6 +5052,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127105209</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4944,6 +5154,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399712</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5054,6 +5269,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129372672</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5159,6 +5379,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373239</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5281,6 +5506,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373573</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5403,6 +5633,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425231</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5500,6 +5735,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399702</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5603,6 +5843,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425252</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5708,6 +5953,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399708</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5811,6 +6061,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373098</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5918,6 +6173,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399684</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6036,6 +6296,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373315</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6142,6 +6407,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399707</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6249,6 +6519,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399713</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6373,6 +6648,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128053525</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6475,6 +6755,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399685</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6590,6 +6875,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874752</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6687,6 +6977,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399727</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6784,8 +7079,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127399728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>